--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task1_empathetic_engagement.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task1_empathetic_engagement.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF42DC-AB8C-471A-B55C-DFA349A7E0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\RLHF\phases\phase2\hh-annotations\results\kallirroi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CABB0B-EB8A-436E-A0A5-8F125457C72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,46 +61,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000077-0001</t>
-  </si>
-  <si>
-    <t>I didn't know there were so many different regions and cultures in Japan.</t>
-  </si>
-  <si>
-    <t>Yes, it's a diverse country with many different regions and cultures.</t>
-  </si>
-  <si>
-    <t>It's true, each region has its own unique culture and customs.</t>
-  </si>
-  <si>
-    <t>Yes, Japan is incredibly diverse and there's so much to discover.</t>
-  </si>
-  <si>
-    <t>Yes, it's a diverse country with many different customs and traditions.</t>
-  </si>
-  <si>
-    <t>Yes, it's a very diverse country.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000153-0001</t>
-  </si>
-  <si>
-    <t>I'm worried my scrapbook won't be as good as some of the ones I've seen online.</t>
-  </si>
-  <si>
-    <t>I understand, it's natural to compare yourself to others.</t>
-  </si>
-  <si>
-    <t>It's natural to compare yourself to others, but remember that scrapbooking is a personal and unique art form.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but remember, scrapbooking is about capturing your memories, not about being perfect.</t>
-  </si>
-  <si>
-    <t>It's natural to compare your work to others, but remember, it's your unique style that makes it special.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but remember that scrapbooking is about the memories and the process, not just the end result.</t>
+    <t>SFTANNO-000059-0001</t>
+  </si>
+  <si>
+    <t>I'm considering a career change. I'm surprised at how open I am to new possibilities.</t>
+  </si>
+  <si>
+    <t>It's exciting to think about new opportunities. What area are you considering?</t>
+  </si>
+  <si>
+    <t>That's a big decision, but it's exciting to explore new horizons.</t>
+  </si>
+  <si>
+    <t>It's exciting to consider new paths. What's sparking this interest?</t>
+  </si>
+  <si>
+    <t>That's a big decision. It's great to see you being open to new things.</t>
+  </si>
+  <si>
+    <t>That's a big decision. What sparked this interest in a career change?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000121-0001</t>
+  </si>
+  <si>
+    <t>The most challenging part was the uncertainty of waiting and not knowing if my paper would be accepted or not.</t>
+  </si>
+  <si>
+    <t>I completely understand how you feel. Waiting can be nerve-wracking.</t>
+  </si>
+  <si>
+    <t>I can understand how that would be tough. It's a long and arduous process.</t>
+  </si>
+  <si>
+    <t>I can imagine how difficult that must have been.</t>
+  </si>
+  <si>
+    <t>I completely understand, it's a nerve-wracking process.</t>
+  </si>
+  <si>
+    <t>That's understandable, it's tough to be in limbo like that.</t>
   </si>
   <si>
     <t>SFTANNO-000019-0001</t>
@@ -161,46 +166,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable.</t>
   </si>
   <si>
-    <t>SFTANNO-000131-0001</t>
-  </si>
-  <si>
-    <t>I've always dreamed of visiting Japan, but I'm afraid of the language barrier.</t>
-  </si>
-  <si>
-    <t>I can understand your concern.</t>
-  </si>
-  <si>
-    <t>I can understand the apprehension.</t>
-  </si>
-  <si>
-    <t>Japan is a fascinating country, but language can be a challenge.</t>
-  </si>
-  <si>
-    <t>It's a unique and fascinating country.</t>
-  </si>
-  <si>
-    <t>Japan is a beautiful country.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000058-0001</t>
-  </si>
-  <si>
-    <t>I heard a rumor that the COVID-19 vaccine makes you infertile, is that true?</t>
-  </si>
-  <si>
-    <t>No, that's a false claim, and it's been debunked by scientists.</t>
-  </si>
-  <si>
-    <t>That's a myth that has been debunked by experts.</t>
-  </si>
-  <si>
-    <t>No, that's a myth with no scientific basis. The vaccine is safe for all adults.</t>
-  </si>
-  <si>
-    <t>No, that's a myth. The vaccine doesn't affect fertility in any way.</t>
-  </si>
-  <si>
-    <t>No, that's not true. The vaccine has gone through extensive testing and has been proven safe.</t>
+    <t>SFTANNO-000100-0001</t>
+  </si>
+  <si>
+    <t>Look at all these vintage arcade games! I didn't expect to see so many.</t>
+  </si>
+  <si>
+    <t>Yes, they're quite rare and unique.</t>
+  </si>
+  <si>
+    <t>Yes, it's great to see a collection of classic arcade games.</t>
+  </si>
+  <si>
+    <t>Yes, they have a great selection of classic games.</t>
+  </si>
+  <si>
+    <t>It's amazing how they've preserved the classics.</t>
+  </si>
+  <si>
+    <t>Wow, that's impressive! It's exciting to see all these old games.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000057-0001</t>
+  </si>
+  <si>
+    <t>I've been practicing mindfulness meditation and it's been a really positive experience.</t>
+  </si>
+  <si>
+    <t>That's great to hear! I've been wanting to try it.</t>
+  </si>
+  <si>
+    <t>That's great to hear. What benefits have you noticed from practicing it?</t>
+  </si>
+  <si>
+    <t>That's great to hear. It can be really helpful in reducing stress.</t>
+  </si>
+  <si>
+    <t>That's great to hear! It's so important to take care of our mental health.</t>
+  </si>
+  <si>
+    <t>That's great to hear! How has it been helping you?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0001</t>
@@ -224,151 +229,151 @@
     <t>That's a great idea.</t>
   </si>
   <si>
-    <t>SFTANNO-000098-0001</t>
-  </si>
-  <si>
-    <t>Have you ever ridden in an autonomous vehicle before?</t>
-  </si>
-  <si>
-    <t>No, I haven't had the chance yet.</t>
-  </si>
-  <si>
-    <t>No, but I'm curious to try it out sometime.</t>
-  </si>
-  <si>
-    <t>Yes, I have. It was a really smooth ride.</t>
-  </si>
-  <si>
-    <t>No, I haven't had the chance to yet.</t>
-  </si>
-  <si>
-    <t>No, I haven't.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000050-0001</t>
-  </si>
-  <si>
-    <t>I'm open to anything at this point.</t>
-  </si>
-  <si>
-    <t>That's great!</t>
-  </si>
-  <si>
-    <t>That's a good attitude to have.</t>
-  </si>
-  <si>
-    <t>That's the right attitude.</t>
-  </si>
-  <si>
-    <t>That's a great attitude to have.</t>
-  </si>
-  <si>
-    <t>That's the spirit!</t>
-  </si>
-  <si>
-    <t>SFTANNO-000078-0001</t>
-  </si>
-  <si>
-    <t>I'm worried about cultural misunderstandings when I visit my parents' homeland.</t>
-  </si>
-  <si>
-    <t>It's natural to have concerns about cultural differences, but they can also lead to rich experiences and learning.</t>
-  </si>
-  <si>
-    <t>It's natural to worry about cultural differences, but with some research and preparation, you can have a great experience.</t>
-  </si>
-  <si>
-    <t>That's a valid concern, but it's important to remember that cultural differences are a natural part of any travel experience.</t>
-  </si>
-  <si>
-    <t>It's normal to have those concerns, but remember that everyone is different and that cultural differences can be enriching.</t>
-  </si>
-  <si>
-    <t>It's natural to have concerns, but with proper research and an open mind, you can have a positive experience.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000095-0001</t>
-  </si>
-  <si>
-    <t>Yes, I have. I was so frustrated that the seat was uncomfortable and the entertainment system was broken.</t>
-  </si>
-  <si>
-    <t>That's terrible. I hate when that happens.</t>
-  </si>
-  <si>
-    <t>Ugh, I hate when that happens. It can really ruin the experience.</t>
-  </si>
-  <si>
-    <t>That's terrible! I hate when the entertainment system isn't working.</t>
-  </si>
-  <si>
-    <t>That sounds terrible. It's unacceptable when airlines don't prioritize customer satisfaction.</t>
-  </si>
-  <si>
-    <t>That's so annoying! I've had similar experiences.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000139-0001</t>
-  </si>
-  <si>
-    <t>I'm scared my children are spending too much time online.</t>
-  </si>
-  <si>
-    <t>It's important to monitor their online activity and set boundaries.</t>
-  </si>
-  <si>
-    <t>It's a valid concern, there are so many risks.</t>
-  </si>
-  <si>
-    <t>It's a valid concern, especially with all the dangers online.</t>
-  </si>
-  <si>
-    <t>It's a valid concern, especially with all the content out there.</t>
-  </si>
-  <si>
-    <t>It's important to monitor their online activity.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000130-0001</t>
-  </si>
-  <si>
-    <t>One episode covered the injustices faced by indigenous communities in regard to traditional plant knowledge and genetics research.</t>
-  </si>
-  <si>
-    <t>That's a frustrating and complicated issue.</t>
-  </si>
-  <si>
-    <t>That's a really important issue that needs to be addressed.</t>
-  </si>
-  <si>
-    <t>That's a terrible situation.</t>
-  </si>
-  <si>
-    <t>That's upsetting to hear.</t>
-  </si>
-  <si>
-    <t>That's a serious issue that needs to be addressed.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000073-0001</t>
-  </si>
-  <si>
-    <t>I saw a video of a robot dancing and it was just strange to watch.</t>
-  </si>
-  <si>
-    <t>I agree, it's not really human-like movement.</t>
-  </si>
-  <si>
-    <t>I can imagine. Robots are just not meant to dance.</t>
-  </si>
-  <si>
-    <t>I can imagine. It's almost like they're taking away the uniqueness of human dance.</t>
-  </si>
-  <si>
-    <t>I agree, it's kind of unsettling to see robots mimicking human behavior.</t>
-  </si>
-  <si>
-    <t>I can imagine. It's not something I'd want to watch either.</t>
+    <t>SFTANNO-000074-0001</t>
+  </si>
+  <si>
+    <t>Did you know some astronauts experience a "pale blue dot" effect after seeing earth in space?</t>
+  </si>
+  <si>
+    <t>That's interesting, I wonder what that experience is like.</t>
+  </si>
+  <si>
+    <t>That's interesting, I didn't know that.</t>
+  </si>
+  <si>
+    <t>That's interesting. It's amazing how the view from space can make us appreciate our home more.</t>
+  </si>
+  <si>
+    <t>No, I didn't. That's interesting.</t>
+  </si>
+  <si>
+    <t>Yes, it's a humbling experience that makes you appreciate our planet even more.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000039-0001</t>
+  </si>
+  <si>
+    <t>I got a promotion at work, but now I have to pay more in taxes!</t>
+  </si>
+  <si>
+    <t>It's a bummer when a pay raise affects your taxes, but at least you have more income to show for it.</t>
+  </si>
+  <si>
+    <t>Congratulations on the promotion! It's great to see you're moving up in your career.</t>
+  </si>
+  <si>
+    <t>Congratulations on your promotion! It's a bittersweet moment when your income increases, but so do your taxes.</t>
+  </si>
+  <si>
+    <t>Congratulations on the promotion! It's great to see your hard work paying off.</t>
+  </si>
+  <si>
+    <t>Congratulations on your promotion! That's a great achievement.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000076-0001</t>
+  </si>
+  <si>
+    <t>I'm scared of the future of our society with all of the environmental issues.</t>
+  </si>
+  <si>
+    <t>It's a valid concern. The future of our planet is at stake.</t>
+  </si>
+  <si>
+    <t>It's definitely a cause for concern.</t>
+  </si>
+  <si>
+    <t>I share your concern for the future of our planet.</t>
+  </si>
+  <si>
+    <t>It's understandable to feel that way with the state of the planet.</t>
+  </si>
+  <si>
+    <t>It's definitely a concerning issue that needs to be addressed urgently.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000088-0001</t>
+  </si>
+  <si>
+    <t>Honestly, it was stressful at times, but overall it was a great experience.</t>
+  </si>
+  <si>
+    <t>That's understandable, team sports can be tough.</t>
+  </si>
+  <si>
+    <t>I can imagine, the pressure to perform can be overwhelming.</t>
+  </si>
+  <si>
+    <t>It's understandable that sports can be stressful at times.</t>
+  </si>
+  <si>
+    <t>I can understand why it would be stressful.</t>
+  </si>
+  <si>
+    <t>I can understand how the pressure to perform well could be frustrating.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000115-0001</t>
+  </si>
+  <si>
+    <t>Not yet, but I'm open to suggestions.</t>
+  </si>
+  <si>
+    <t>I understand your apprehension. But, there are many resources out there that could help you.</t>
+  </si>
+  <si>
+    <t>Maybe try taking a walk in nature, or listening to calming music.</t>
+  </si>
+  <si>
+    <t>It's okay to try new things and explore what works for you.</t>
+  </si>
+  <si>
+    <t>It might be helpful to start small with things like taking a walk outside or reading a book.</t>
+  </si>
+  <si>
+    <t>I understand. It can be scary to try new things.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000109-0001</t>
+  </si>
+  <si>
+    <t>I would need some help actually. The grill is such a hassle to set up and I'm already getting overwhelmed.</t>
+  </si>
+  <si>
+    <t>I know what you mean, grilling can be a lot of work. But once everything is set up, it's pretty easy to cook everything.</t>
+  </si>
+  <si>
+    <t>I can help you get it set up. It can be a bit of a hassle, but it's worth it for a good BBQ.</t>
+  </si>
+  <si>
+    <t>I can understand why that would be frustrating. Let's get everything set up together.</t>
+  </si>
+  <si>
+    <t>No problem at all. I'll help you get everything set up.</t>
+  </si>
+  <si>
+    <t>I totally get it. Grilling can be a pain sometimes.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000068-0001</t>
+  </si>
+  <si>
+    <t>Ugh, I hate algebra.</t>
+  </si>
+  <si>
+    <t>I know what you mean, algebra can be frustrating.</t>
+  </si>
+  <si>
+    <t>I know what you mean, it can be a challenging subject.</t>
+  </si>
+  <si>
+    <t>I know the feeling, it can be really difficult.</t>
+  </si>
+  <si>
+    <t>I get it, algebra can be tough.</t>
+  </si>
+  <si>
+    <t>I get it, it can be tough to get through.</t>
   </si>
   <si>
     <t>SFTANNO-000018-0001</t>
@@ -392,46 +397,46 @@
     <t>It is incredible, isn't it?</t>
   </si>
   <si>
-    <t>SFTANNO-000105-0001</t>
-  </si>
-  <si>
-    <t>I don't like this cold and gloomy weather.</t>
-  </si>
-  <si>
-    <t>I completely understand, it's so depressing.</t>
-  </si>
-  <si>
-    <t>I know, it's so depressing.</t>
-  </si>
-  <si>
-    <t>I know, it's really depressing.</t>
-  </si>
-  <si>
-    <t>Me neither, it makes me feel so unmotivated.</t>
-  </si>
-  <si>
-    <t>I know, it's hard to stay motivated in this weather.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000154-0001</t>
-  </si>
-  <si>
-    <t>My partner keeps criticizing how I chop vegetables, it's driving me insane.</t>
-  </si>
-  <si>
-    <t>Ugh, I hate when people criticize our cooking methods.</t>
-  </si>
-  <si>
-    <t>That's so frustrating, they should be more supportive.</t>
-  </si>
-  <si>
-    <t>That's so frustrating, it's not your fault if they can't cut their own veggies.</t>
-  </si>
-  <si>
-    <t>That's so frustrating, everyone has their own way of doing things.</t>
-  </si>
-  <si>
-    <t>That's frustrating, they should trust your skills in the kitchen.</t>
+    <t>SFTANNO-000092-0001</t>
+  </si>
+  <si>
+    <t>I used to love going out on my boat, but it's too expensive to maintain now.</t>
+  </si>
+  <si>
+    <t>That's so sad to hear. It's unfortunate that it's not financially feasible anymore.</t>
+  </si>
+  <si>
+    <t>That's too bad, I know how much you loved being on the water.</t>
+  </si>
+  <si>
+    <t>I know how you feel. It's tough to keep up with the costs of boat ownership.</t>
+  </si>
+  <si>
+    <t>I can understand why it would be difficult to keep up with the costs.</t>
+  </si>
+  <si>
+    <t>I'm sorry to hear that. It's such a shame that so many people can't enjoy boating because of the cost.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000140-0001</t>
+  </si>
+  <si>
+    <t>I'm so frustrated that my computer keeps crashing.</t>
+  </si>
+  <si>
+    <t>I know how you feel, it's so infuriating when technology fails us.</t>
+  </si>
+  <si>
+    <t>It's infuriating when technology doesn't work as it should.</t>
+  </si>
+  <si>
+    <t>That's so annoying, have you tried updating your software?</t>
+  </si>
+  <si>
+    <t>Computer crashes can be so infuriating.</t>
+  </si>
+  <si>
+    <t>That's really annoying, have you tried running a virus scan?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0001</t>
@@ -476,25 +481,25 @@
     <t>It's such a difficult balance.</t>
   </si>
   <si>
-    <t>SFTANNO-000118-0001</t>
-  </si>
-  <si>
-    <t>We can support local community clinics and increase our involvement in community-based programs that advocate for health equity.</t>
-  </si>
-  <si>
-    <t>Yes, these initiatives are crucial in promoting health equity and ensuring that everyone has access to quality healthcare.</t>
-  </si>
-  <si>
-    <t>That's a fantastic idea! It's great to see people coming together to make a positive impact on the healthcare system.</t>
-  </si>
-  <si>
-    <t>That's a fantastic idea, and it's uplifting to know that we can make a difference in our own community.</t>
-  </si>
-  <si>
-    <t>That's a fantastic idea! It's wonderful to see people taking an active role in promoting health equity.</t>
-  </si>
-  <si>
-    <t>That's a fantastic idea! We can work towards creating a more inclusive healthcare system by supporting these initiatives.</t>
+    <t>SFTANNO-000069-0001</t>
+  </si>
+  <si>
+    <t>Yes, I love supporting Leave No Trace and the Sustainable Travel International.</t>
+  </si>
+  <si>
+    <t>That's great to hear! It's always good to support organizations that prioritize environmental protection.</t>
+  </si>
+  <si>
+    <t>Those are great choices! It's so fulfilling to support organizations that prioritize sustainability.</t>
+  </si>
+  <si>
+    <t>Those are great organizations to support. It's wonderful to see people taking initiative to protect the environment.</t>
+  </si>
+  <si>
+    <t>Those are great organizations! It's so important to support those who prioritize sustainability in the outdoors.</t>
+  </si>
+  <si>
+    <t>Those are great organizations to support. It's important to invest in eco-friendly practices to protect the environment.</t>
   </si>
 </sst>
 </file>
@@ -513,7 +518,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -862,14 +866,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="13" width="27.42578125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.109375" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -933,22 +937,22 @@
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -965,19 +969,19 @@
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
@@ -986,7 +990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -997,34 +1001,34 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1035,7 +1039,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
@@ -1053,16 +1057,16 @@
         <v>39</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1073,19 +1077,19 @@
         <v>43</v>
       </c>
       <c r="D6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
@@ -1100,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1111,34 +1115,34 @@
         <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L7" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1155,13 +1159,13 @@
         <v>58</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H8" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
@@ -1173,10 +1177,10 @@
         <v>61</v>
       </c>
       <c r="L8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1187,25 +1191,25 @@
         <v>64</v>
       </c>
       <c r="D9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
@@ -1214,7 +1218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1225,25 +1229,25 @@
         <v>71</v>
       </c>
       <c r="D10" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
@@ -1252,7 +1256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1263,34 +1267,34 @@
         <v>78</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J11" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="L11" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1307,28 +1311,28 @@
         <v>86</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="L12" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1339,34 +1343,34 @@
         <v>92</v>
       </c>
       <c r="D13" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J13" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
       <c r="L13" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1377,34 +1381,34 @@
         <v>99</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="L14" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1421,7 +1425,7 @@
         <v>107</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
@@ -1433,7 +1437,7 @@
         <v>109</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
@@ -1442,7 +1446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1453,34 +1457,34 @@
         <v>113</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
       <c r="J16" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
       <c r="L16" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1497,19 +1501,19 @@
         <v>121</v>
       </c>
       <c r="F17" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
       <c r="H17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
       <c r="J17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
@@ -1518,7 +1522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1529,34 +1533,34 @@
         <v>127</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
       <c r="F18" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
       <c r="H18" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
       <c r="J18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
       <c r="L18" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1573,28 +1577,28 @@
         <v>135</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
       <c r="H19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
       <c r="L19" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1605,34 +1609,34 @@
         <v>141</v>
       </c>
       <c r="D20" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
       <c r="H20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
       <c r="L20" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1643,13 +1647,13 @@
         <v>148</v>
       </c>
       <c r="D21" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
@@ -1661,16 +1665,16 @@
         <v>151</v>
       </c>
       <c r="J21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1681,36 +1685,36 @@
         <v>155</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
       <c r="J22" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
       <c r="L22" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{266B148C-F1A9-469E-AAC0-7C3D5F1A6E36}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J22 D2:D22 F2:F22 H2:H22 L2:L22" xr:uid="{9ACEF345-8526-40E6-ACE0-A8F82B7EDB81}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
